--- a/output/pdf_financials_xlsx/ESM.xlsx
+++ b/output/pdf_financials_xlsx/ESM.xlsx
@@ -1297,19 +1297,19 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>5.085271</v>
+        <v>-5.085271</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>9.357562</v>
+        <v>0</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>5.781431</v>
+        <v>-5.445089</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>45.282488</v>
+        <v>-44.537966</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>66.92061099999999</v>
+        <v>0.170345</v>
       </c>
       <c r="G16" s="3" t="n">
         <v>-99.562676</v>
@@ -1593,19 +1593,19 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>5.085271</v>
+        <v>-5.085271</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>4.678781</v>
+        <v>-4.678781</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>5.61326</v>
+        <v>-5.61326</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>44.910227</v>
+        <v>-44.910227</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>33.375133</v>
+        <v>-33.375133</v>
       </c>
       <c r="G20" s="3" t="n">
         <v>-50.011563</v>
@@ -1776,19 +1776,19 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>5.085271</v>
+        <v>-5.085271</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>4.678781</v>
+        <v>-4.678781</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>5.61326</v>
+        <v>-5.61326</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>44.910227</v>
+        <v>-44.910227</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>33.375133</v>
+        <v>-33.375133</v>
       </c>
       <c r="G23" s="3" t="n">
         <v>-50.011563</v>
@@ -1959,19 +1959,19 @@
         </is>
       </c>
       <c r="B26" s="3" t="n">
-        <v>127.131775</v>
+        <v>-127.131775</v>
       </c>
       <c r="C26" s="3" t="n">
-        <v>233.93905</v>
+        <v>-233.93905</v>
       </c>
       <c r="D26" s="3" t="n">
-        <v>280.663</v>
+        <v>-280.663</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>-408.274791</v>
+        <v>408.274791</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>556.252217</v>
+        <v>-556.252217</v>
       </c>
       <c r="G26" s="3" t="n">
         <v>625.144538</v>
@@ -2020,19 +2020,19 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>5.085271</v>
+        <v>-5.085271</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>9.357562</v>
+        <v>0</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>5.781431</v>
+        <v>-5.445089</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>45.282488</v>
+        <v>-44.537966</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>66.92061099999999</v>
+        <v>0.170345</v>
       </c>
       <c r="G27" s="3" t="n">
         <v>-99.562676</v>
@@ -2142,19 +2142,19 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>5.085271</v>
+        <v>-5.085271</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>9.357562</v>
+        <v>0</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>5.800305</v>
+        <v>-5.426215</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>45.362176</v>
+        <v>-44.458278</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>67.04391800000001</v>
+        <v>0.293652</v>
       </c>
       <c r="G29" s="3" t="n">
         <v>-99.428009</v>
@@ -2288,19 +2288,21 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C31" s="3" t="n">
-        <v>50</v>
+        <v>-0</v>
+      </c>
+      <c r="C31" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D31" s="3" t="n">
-        <v>2.908812714360856</v>
+        <v>-3.08848946270667</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>0.8220860125883543</v>
+        <v>-0.8358284704784228</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>50.12727394255262</v>
+        <v>19692.66958231824</v>
       </c>
       <c r="G31" s="3" t="n">
         <v>-49.76876374837494</v>
@@ -6056,13 +6058,13 @@
         </is>
       </c>
       <c r="B99" s="3" t="n">
-        <v>5.085271</v>
+        <v>-5.085271</v>
       </c>
       <c r="C99" s="3" t="n">
-        <v>4.678781</v>
+        <v>-4.678781</v>
       </c>
       <c r="D99" s="3" t="n">
-        <v>5.61326</v>
+        <v>-5.61326</v>
       </c>
       <c r="E99" s="3" t="n">
         <v>-44.910227</v>
@@ -63666,10 +63668,10 @@
         </is>
       </c>
       <c r="I580" s="5" t="n">
-        <v>33.375133</v>
+        <v>-33.375133</v>
       </c>
       <c r="J580" s="5" t="n">
-        <v>50.011563</v>
+        <v>-50.011563</v>
       </c>
       <c r="K580" s="5" t="n">
         <v>-214.468409</v>
@@ -68552,16 +68554,16 @@
         </is>
       </c>
       <c r="G632" s="5" t="n">
-        <v>3.228945</v>
+        <v>-3.228945</v>
       </c>
       <c r="H632" s="5" t="n">
-        <v>46.046382</v>
+        <v>-46.046382</v>
       </c>
       <c r="I632" s="5" t="n">
-        <v>30.19429</v>
+        <v>-30.19429</v>
       </c>
       <c r="J632" s="5" t="n">
-        <v>56.293316</v>
+        <v>-56.293316</v>
       </c>
       <c r="K632" t="inlineStr">
         <is>
@@ -69865,10 +69867,10 @@
         </is>
       </c>
       <c r="H646" s="5" t="n">
-        <v>44.910227</v>
+        <v>-44.910227</v>
       </c>
       <c r="I646" s="5" t="n">
-        <v>33.375133</v>
+        <v>-33.375133</v>
       </c>
       <c r="J646" t="inlineStr">
         <is>
@@ -70155,10 +70157,10 @@
         </is>
       </c>
       <c r="H649" s="5" t="n">
-        <v>46.046382</v>
+        <v>-46.046382</v>
       </c>
       <c r="I649" s="5" t="n">
-        <v>30.19429</v>
+        <v>-30.19429</v>
       </c>
       <c r="J649" t="inlineStr">
         <is>
@@ -71766,10 +71768,10 @@
         </is>
       </c>
       <c r="G666" s="5" t="n">
-        <v>5.61326</v>
+        <v>-5.61326</v>
       </c>
       <c r="H666" s="5" t="n">
-        <v>44.910227</v>
+        <v>-44.910227</v>
       </c>
       <c r="I666" t="inlineStr">
         <is>
@@ -74447,10 +74449,10 @@
         </is>
       </c>
       <c r="F694" s="5" t="n">
-        <v>4.678781</v>
+        <v>-4.678781</v>
       </c>
       <c r="G694" s="5" t="n">
-        <v>5.943761</v>
+        <v>-5.943761</v>
       </c>
       <c r="H694" t="inlineStr">
         <is>
@@ -77694,10 +77696,10 @@
         </is>
       </c>
       <c r="E728" s="5" t="n">
-        <v>5.085271</v>
+        <v>-5.085271</v>
       </c>
       <c r="F728" s="5" t="n">
-        <v>4.678781</v>
+        <v>-4.678781</v>
       </c>
       <c r="G728" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/ESM.xlsx
+++ b/output/pdf_financials_xlsx/ESM.xlsx
@@ -1053,10 +1053,10 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>-0.406286</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>-0.04079</v>
       </c>
       <c r="D12" s="3" t="n">
         <v>0</v>
@@ -1080,10 +1080,10 @@
         <v>0</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>-0.022085</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>-0.001755</v>
       </c>
       <c r="M12" s="1" t="inlineStr">
         <is>
@@ -1091,10 +1091,10 @@
         </is>
       </c>
       <c r="N12" s="3" t="n">
-        <v>0</v>
+        <v>-0.035818</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>0</v>
+        <v>-1.5e-05</v>
       </c>
       <c r="P12" s="1" t="inlineStr">
         <is>
@@ -2020,10 +2020,10 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-5.085271</v>
+        <v>-4.678985</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>0</v>
+        <v>0.04079</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>-5.445089</v>
@@ -2047,10 +2047,10 @@
         <v>219.885066</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-6.243881</v>
+        <v>-6.221796</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>-7.21577</v>
+        <v>-7.214015</v>
       </c>
       <c r="M27" s="1" t="inlineStr">
         <is>
@@ -2058,10 +2058,10 @@
         </is>
       </c>
       <c r="N27" s="3" t="n">
-        <v>-10.900424</v>
+        <v>-10.864606</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>-7.559634</v>
+        <v>-7.559619</v>
       </c>
       <c r="P27" s="1" t="inlineStr">
         <is>
@@ -2142,10 +2142,10 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-5.085271</v>
+        <v>-4.678985</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>0</v>
+        <v>0.04079</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>-5.426215</v>
@@ -2169,10 +2169,10 @@
         <v>219.929114</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-6.236186</v>
+        <v>-6.214101</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-7.21577</v>
+        <v>-7.214015</v>
       </c>
       <c r="M29" s="1" t="inlineStr">
         <is>
@@ -2180,10 +2180,10 @@
         </is>
       </c>
       <c r="N29" s="3" t="n">
-        <v>-10.900424</v>
+        <v>-10.864606</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>-7.559634</v>
+        <v>-7.559619</v>
       </c>
       <c r="P29" s="1" t="inlineStr">
         <is>
@@ -2485,10 +2485,10 @@
         <v>0.912666</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>0.045024</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0</v>
+        <v>0.116347</v>
       </c>
     </row>
     <row r="35">
@@ -2595,10 +2595,10 @@
         <v>0.912666</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0</v>
+        <v>0.045024</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0</v>
+        <v>0.116347</v>
       </c>
     </row>
     <row r="37">
@@ -3255,10 +3255,10 @@
         <v>0.267679</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>0.421313</v>
+        <v>0.376289</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>0.489544</v>
+        <v>0.373197</v>
       </c>
     </row>
     <row r="49">
@@ -8784,7 +8784,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -62794,7 +62794,11 @@
           <t>General and administrative expenses 13(a)</t>
         </is>
       </c>
-      <c r="D571" t="inlineStr"/>
+      <c r="D571" t="inlineStr">
+        <is>
+          <t>GeneralAndAdministrativeExpense</t>
+        </is>
+      </c>
       <c r="E571" t="inlineStr">
         <is>
           <t>-</t>
@@ -65432,7 +65436,11 @@
           <t>General and administrative expenses 11(a)</t>
         </is>
       </c>
-      <c r="D599" t="inlineStr"/>
+      <c r="D599" t="inlineStr">
+        <is>
+          <t>GeneralAndAdministrativeExpense</t>
+        </is>
+      </c>
       <c r="E599" t="inlineStr">
         <is>
           <t>-</t>
@@ -67606,7 +67614,11 @@
           <t>General and administrative expenses 11(a)</t>
         </is>
       </c>
-      <c r="D622" t="inlineStr"/>
+      <c r="D622" t="inlineStr">
+        <is>
+          <t>GeneralAndAdministrativeExpense</t>
+        </is>
+      </c>
       <c r="E622" t="inlineStr">
         <is>
           <t>-</t>
@@ -77204,7 +77216,7 @@
       </c>
       <c r="D723" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E723" s="5" t="n">

--- a/output/pdf_financials_xlsx/ESM.xlsx
+++ b/output/pdf_financials_xlsx/ESM.xlsx
@@ -773,10 +773,10 @@
         <v>0</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>2.420837</v>
+        <v>2.631581</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>1.544895</v>
+        <v>1.738267</v>
       </c>
       <c r="M7" s="1" t="inlineStr">
         <is>
@@ -784,10 +784,10 @@
         </is>
       </c>
       <c r="N7" s="3" t="n">
-        <v>1.483521</v>
+        <v>1.632574</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>1.161882</v>
+        <v>1.223376</v>
       </c>
       <c r="P7" s="1" t="inlineStr">
         <is>
@@ -956,10 +956,10 @@
         <v>0</v>
       </c>
       <c r="K10" s="3" t="n">
-        <v>2.420837</v>
+        <v>2.631581</v>
       </c>
       <c r="L10" s="3" t="n">
-        <v>1.544895</v>
+        <v>1.738267</v>
       </c>
       <c r="M10" s="1" t="inlineStr">
         <is>
@@ -967,10 +967,10 @@
         </is>
       </c>
       <c r="N10" s="3" t="n">
-        <v>1.483521</v>
+        <v>1.632574</v>
       </c>
       <c r="O10" s="3" t="n">
-        <v>1.161882</v>
+        <v>1.223376</v>
       </c>
       <c r="P10" s="1" t="inlineStr">
         <is>
@@ -1019,10 +1019,10 @@
         <v>0</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>-2.420837</v>
+        <v>-2.631581</v>
       </c>
       <c r="L11" s="3" t="n">
-        <v>-1.544895</v>
+        <v>-1.738267</v>
       </c>
       <c r="M11" s="1" t="inlineStr">
         <is>
@@ -1030,10 +1030,10 @@
         </is>
       </c>
       <c r="N11" s="3" t="n">
-        <v>-1.483521</v>
+        <v>-1.632574</v>
       </c>
       <c r="O11" s="3" t="n">
-        <v>-1.161882</v>
+        <v>-1.223376</v>
       </c>
       <c r="P11" s="1" t="inlineStr">
         <is>
@@ -4310,40 +4310,40 @@
         <v>0</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>0</v>
+        <v>5.045061</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>0</v>
+        <v>10.571297</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>0</v>
+        <v>5.613512</v>
       </c>
       <c r="I67" s="3" t="n">
-        <v>0</v>
+        <v>0.260577</v>
       </c>
       <c r="J67" s="3" t="n">
-        <v>0</v>
+        <v>0.748068</v>
       </c>
       <c r="K67" s="3" t="n">
-        <v>0</v>
+        <v>0.480916</v>
       </c>
       <c r="L67" s="3" t="n">
-        <v>0</v>
+        <v>0.07555199999999999</v>
       </c>
       <c r="M67" s="3" t="n">
-        <v>0</v>
+        <v>0.12147</v>
       </c>
       <c r="N67" s="3" t="n">
-        <v>0</v>
+        <v>1.328971</v>
       </c>
       <c r="O67" s="3" t="n">
-        <v>0</v>
+        <v>1.459307</v>
       </c>
       <c r="P67" s="3" t="n">
-        <v>0</v>
+        <v>1.096015</v>
       </c>
       <c r="Q67" s="3" t="n">
-        <v>0</v>
+        <v>1.080369</v>
       </c>
     </row>
     <row r="68">
@@ -4365,40 +4365,40 @@
         <v>5.397855</v>
       </c>
       <c r="F68" s="3" t="n">
-        <v>8.531931999999999</v>
+        <v>13.576993</v>
       </c>
       <c r="G68" s="3" t="n">
-        <v>24.670145</v>
+        <v>35.241442</v>
       </c>
       <c r="H68" s="3" t="n">
-        <v>16.2415</v>
+        <v>21.855012</v>
       </c>
       <c r="I68" s="3" t="n">
-        <v>0.703369</v>
+        <v>0.963946</v>
       </c>
       <c r="J68" s="3" t="n">
-        <v>0.851003</v>
+        <v>1.599071</v>
       </c>
       <c r="K68" s="3" t="n">
-        <v>0.594762</v>
+        <v>1.075678</v>
       </c>
       <c r="L68" s="3" t="n">
-        <v>0.501538</v>
+        <v>0.57709</v>
       </c>
       <c r="M68" s="3" t="n">
-        <v>1.996929</v>
+        <v>2.118399</v>
       </c>
       <c r="N68" s="3" t="n">
-        <v>2.405341</v>
+        <v>3.734312</v>
       </c>
       <c r="O68" s="3" t="n">
-        <v>3.121777</v>
+        <v>4.581084</v>
       </c>
       <c r="P68" s="3" t="n">
-        <v>2.905387</v>
+        <v>4.001402</v>
       </c>
       <c r="Q68" s="3" t="n">
-        <v>2.590828</v>
+        <v>3.671197</v>
       </c>
     </row>
     <row r="69">
@@ -4750,13 +4750,13 @@
         <v>1.713246</v>
       </c>
       <c r="F75" s="3" t="n">
-        <v>7.863024</v>
+        <v>2.817963</v>
       </c>
       <c r="G75" s="3" t="n">
-        <v>131.352082</v>
+        <v>120.780785</v>
       </c>
       <c r="H75" s="3" t="n">
-        <v>232.899617</v>
+        <v>227.286105</v>
       </c>
       <c r="I75" s="3" t="n">
         <v>0</v>
@@ -4765,19 +4765,19 @@
         <v>0</v>
       </c>
       <c r="K75" s="3" t="n">
-        <v>0.037546</v>
+        <v>0</v>
       </c>
       <c r="L75" s="3" t="n">
-        <v>0.994703</v>
+        <v>0.9191510000000001</v>
       </c>
       <c r="M75" s="3" t="n">
-        <v>1.327742</v>
+        <v>1.206272</v>
       </c>
       <c r="N75" s="3" t="n">
-        <v>0.8412500000000001</v>
+        <v>0</v>
       </c>
       <c r="O75" s="3" t="n">
-        <v>2.541395</v>
+        <v>1.082088</v>
       </c>
       <c r="P75" s="3" t="n">
         <v>0</v>
@@ -6813,13 +6813,13 @@
         <v>0</v>
       </c>
       <c r="H110" s="3" t="n">
-        <v>0</v>
+        <v>0.065804</v>
       </c>
       <c r="I110" s="3" t="n">
-        <v>0</v>
+        <v>0.26322</v>
       </c>
       <c r="J110" s="3" t="n">
-        <v>0</v>
+        <v>0.08774</v>
       </c>
       <c r="K110" s="3" t="n">
         <v>0</v>
@@ -32648,7 +32648,11 @@
           <t>Accretion</t>
         </is>
       </c>
-      <c r="D253" t="inlineStr"/>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E253" t="inlineStr">
         <is>
           <t>-</t>
@@ -34646,7 +34650,11 @@
           <t>Proceeds from private placement (Note 10)</t>
         </is>
       </c>
-      <c r="D274" t="inlineStr"/>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E274" t="inlineStr">
         <is>
           <t>-</t>
@@ -38448,7 +38456,11 @@
           <t>Accretion</t>
         </is>
       </c>
-      <c r="D314" t="inlineStr"/>
+      <c r="D314" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E314" t="inlineStr">
         <is>
           <t>-</t>
